--- a/support/Dataset_S8_ReAct.xlsx
+++ b/support/Dataset_S8_ReAct.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnoutb-my.sharepoint.com/personal/epuerta_utb_edu_co/Documents/Academic/AI Literacy/support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_4EDB9F5FBC0224540622DE20EC1E1E29A6D174A0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06AD341E-1620-468D-8307-886C4B2AA41B}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_4EDB9F5FBC0224540622DE20EC1E1E29A6D174A0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50951D9A-54DA-4FC1-BB5F-3692AA27D40F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tickets_portal_academico" sheetId="1" r:id="rId1"/>
@@ -820,7 +820,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -948,6 +948,12 @@
       <color rgb="FF231F20"/>
       <name val="Calibri"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF231F20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -1105,199 +1111,203 @@
   </cellStyleXfs>
   <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1580,666 +1590,666 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="58" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
     </row>
     <row r="3" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="6">
         <v>48</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="4">
         <v>1</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="10">
         <v>12</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H6" s="8">
         <v>0</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="I6" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="4">
         <v>6</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="4">
         <v>2</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="8">
         <v>4</v>
       </c>
-      <c r="H8" s="16">
+      <c r="H8" s="8">
         <v>0</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="13">
         <v>18</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="4">
         <v>1</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="10">
         <v>36</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="14">
         <v>3</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="4">
         <v>8</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="4">
         <v>0</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="8">
         <v>2</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="8">
         <v>0</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="15" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="4">
         <v>1</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="4">
         <v>0</v>
       </c>
-      <c r="I13" s="12" t="s">
+      <c r="I13" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="10">
         <v>24</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="8">
         <v>0</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="4">
         <v>10</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="4">
         <v>0</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="17" t="s">
+      <c r="F16" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="10">
         <v>30</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="8">
         <v>1</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="4">
         <v>5</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="4">
         <v>2</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="I17" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="17" t="s">
+      <c r="F18" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="8">
         <v>3</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="8">
         <v>1</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="13">
         <v>15</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="4">
         <v>0</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="F20" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="8">
         <v>7</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="8">
         <v>0</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="I20" s="15" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="6">
         <v>72</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="17">
         <v>4</v>
       </c>
-      <c r="I21" s="25" t="s">
+      <c r="I21" s="17" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="8">
         <v>9</v>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="8">
         <v>0</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="12" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="13">
         <v>16</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="4">
         <v>2</v>
       </c>
-      <c r="I23" s="12" t="s">
+      <c r="I23" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="10">
         <v>20</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="8">
         <v>1</v>
       </c>
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="12" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2270,342 +2280,342 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
     </row>
     <row r="3" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="19" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="20" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="34" t="s">
+      <c r="D5" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="24" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="7" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="28" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="20" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="24" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="17" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="28" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="7" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="32" t="s">
+      <c r="A13" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C13" s="34" t="s">
+      <c r="C13" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="28" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="20" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="C15" s="34" t="s">
+      <c r="C15" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="28" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="17" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="32" t="s">
+      <c r="A17" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="28" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="22" t="s">
         <v>178</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="D18" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="17" t="s">
         <v>180</v>
       </c>
     </row>
@@ -2627,356 +2637,356 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="50" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="5" max="5" width="24.26953125" customWidth="1"/>
+    <col min="6" max="6" width="12" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="61" t="s">
         <v>181</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="62" t="s">
         <v>182</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="B2" s="62"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
     </row>
     <row r="4" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="59" t="s">
         <v>183</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
     </row>
     <row r="5" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="63" t="s">
         <v>184</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="65" t="s">
         <v>185</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
     </row>
     <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-    </row>
-    <row r="7" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="38" t="s">
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
+    </row>
+    <row r="7" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="64" t="s">
         <v>186</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="66" t="s">
         <v>187</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
     </row>
     <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="37" t="s">
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
+    </row>
+    <row r="9" spans="1:6" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="63" t="s">
         <v>188</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="65" t="s">
         <v>189</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="C9" s="65"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+    </row>
+    <row r="10" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="65"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
     </row>
     <row r="11" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="64" t="s">
         <v>190</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="66" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
     </row>
     <row r="14" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="57" t="s">
         <v>192</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
     </row>
     <row r="15" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="39" t="s">
+      <c r="A16" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="31" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="34"/>
     </row>
     <row r="17" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="39" t="s">
+      <c r="A17" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42" t="s">
+      <c r="C17" s="31"/>
+      <c r="D17" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="E17" s="43"/>
-      <c r="F17" s="44"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="34"/>
     </row>
     <row r="18" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="43" t="s">
+      <c r="C18" s="31"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="37" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="48" t="s">
+      <c r="A19" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="52"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="42"/>
     </row>
     <row r="20" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="48" t="s">
+      <c r="A20" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="51" t="s">
+      <c r="C20" s="40"/>
+      <c r="D20" s="41" t="s">
         <v>209</v>
       </c>
-      <c r="E20" s="34"/>
-      <c r="F20" s="52"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="42"/>
     </row>
     <row r="21" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="48" t="s">
+      <c r="A21" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="51"/>
-      <c r="E21" s="34" t="s">
+      <c r="C21" s="40"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="F21" s="54" t="s">
+      <c r="F21" s="44" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="55" t="s">
+      <c r="A22" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="B22" s="56" t="s">
+      <c r="B22" s="46" t="s">
         <v>200</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C22" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="D22" s="58"/>
-      <c r="E22" s="59"/>
-      <c r="F22" s="60"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="50"/>
     </row>
     <row r="23" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="51" t="s">
         <v>202</v>
       </c>
-      <c r="C23" s="57"/>
-      <c r="D23" s="58" t="s">
+      <c r="C23" s="47"/>
+      <c r="D23" s="48" t="s">
         <v>213</v>
       </c>
-      <c r="E23" s="59"/>
-      <c r="F23" s="60"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="50"/>
     </row>
     <row r="24" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="C24" s="57"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="59" t="s">
+      <c r="C24" s="47"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="F24" s="60"/>
+      <c r="F24" s="50"/>
     </row>
     <row r="25" spans="1:6" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="B25" s="61" t="s">
+      <c r="B25" s="51" t="s">
         <v>215</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="C25" s="47" t="s">
         <v>216</v>
       </c>
-      <c r="D25" s="58" t="s">
+      <c r="D25" s="48" t="s">
         <v>217</v>
       </c>
-      <c r="E25" s="59" t="s">
+      <c r="E25" s="49" t="s">
         <v>218</v>
       </c>
-      <c r="F25" s="61" t="s">
+      <c r="F25" s="51" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="59" t="s">
         <v>220</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="60" t="s">
         <v>221</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
+      <c r="B28" s="60"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="60"/>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
+      <c r="A29" s="60"/>
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
     </row>
     <row r="30" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
+      <c r="A30" s="60"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
     </row>
     <row r="31" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
+      <c r="A31" s="60"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B5:F6"/>
+    <mergeCell ref="B7:F8"/>
     <mergeCell ref="B9:F10"/>
     <mergeCell ref="B11:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A28:F31"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B5:F6"/>
-    <mergeCell ref="B7:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3002,336 +3012,336 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="57" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
     </row>
     <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="58" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="2" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="3" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="52" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="4">
         <v>4</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="4">
         <v>2</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="4">
         <v>5</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="4">
         <v>1</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="16" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="54" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="63" t="s">
+      <c r="C6" s="53" t="s">
         <v>241</v>
       </c>
-      <c r="D6" s="63">
+      <c r="D6" s="53">
         <v>3</v>
       </c>
-      <c r="E6" s="63">
+      <c r="E6" s="53">
         <v>1</v>
       </c>
-      <c r="F6" s="63">
+      <c r="F6" s="53">
         <v>3</v>
       </c>
-      <c r="G6" s="63">
+      <c r="G6" s="53">
         <v>0</v>
       </c>
-      <c r="H6" s="65" t="s">
+      <c r="H6" s="55" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="52" t="s">
         <v>242</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="4">
         <v>6</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="4">
         <v>8</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="4">
         <v>2</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="6" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="64" t="s">
+      <c r="B8" s="54" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="53" t="s">
         <v>246</v>
       </c>
-      <c r="D8" s="63">
+      <c r="D8" s="53">
         <v>2</v>
       </c>
-      <c r="E8" s="63">
+      <c r="E8" s="53">
         <v>4</v>
       </c>
-      <c r="F8" s="63">
+      <c r="F8" s="53">
         <v>2</v>
       </c>
-      <c r="G8" s="66">
+      <c r="G8" s="56">
         <v>3</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="6" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="52" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="4">
         <v>5</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="4">
         <v>1</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="4">
         <v>6</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="4">
         <v>0</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="16" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="63" t="s">
+      <c r="A10" s="53" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="54" t="s">
         <v>249</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="53" t="s">
         <v>250</v>
       </c>
-      <c r="D10" s="63">
+      <c r="D10" s="53">
         <v>4</v>
       </c>
-      <c r="E10" s="63">
+      <c r="E10" s="53">
         <v>3</v>
       </c>
-      <c r="F10" s="63">
+      <c r="F10" s="53">
         <v>4</v>
       </c>
-      <c r="G10" s="63">
+      <c r="G10" s="53">
         <v>2</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="6" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B11" s="62" t="s">
+      <c r="B11" s="52" t="s">
         <v>251</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="4">
         <v>7</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="4">
         <v>1</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="4">
         <v>9</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="4">
         <v>0</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="16" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="63" t="s">
+      <c r="A12" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="54" t="s">
         <v>253</v>
       </c>
-      <c r="C12" s="63" t="s">
+      <c r="C12" s="53" t="s">
         <v>238</v>
       </c>
-      <c r="D12" s="63">
+      <c r="D12" s="53">
         <v>3</v>
       </c>
-      <c r="E12" s="63">
+      <c r="E12" s="53">
         <v>2</v>
       </c>
-      <c r="F12" s="63">
+      <c r="F12" s="53">
         <v>3</v>
       </c>
-      <c r="G12" s="63">
+      <c r="G12" s="53">
         <v>2</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="6" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B13" s="62" t="s">
+      <c r="B13" s="52" t="s">
         <v>255</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="4">
         <v>5</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="4">
         <v>0</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="4">
         <v>12</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="4">
         <v>0</v>
       </c>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="16" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="63" t="s">
+      <c r="A14" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="54" t="s">
         <v>257</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="53" t="s">
         <v>241</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="53">
         <v>6</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="53">
         <v>2</v>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="53">
         <v>7</v>
       </c>
-      <c r="G14" s="63">
+      <c r="G14" s="53">
         <v>1</v>
       </c>
-      <c r="H14" s="65" t="s">
+      <c r="H14" s="55" t="s">
         <v>239</v>
       </c>
     </row>
